--- a/sheets/조재수대금교본/검수/긴 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/긴 아리랑.xlsx
@@ -3636,36 +3636,34 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋ʒ
-㳞
-⊏</t>
+          <t xml:space="preserve">湳淋
+㳞</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱㅂ
-–
-ﾉ</t>
+          <t xml:space="preserve">南
+–</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢ʒ
+          <t xml:space="preserve">汰潢
 南潢</t>
         </is>
       </c>
@@ -3678,14 +3676,13 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
-Z</t>
+          <t xml:space="preserve">汰潢</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3706,8 +3703,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ汰潢
-Z</t>
+          <t xml:space="preserve">汰潢</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3716,13 +3712,13 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–И·</t>
+–·</t>
         </is>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 林南</t>
         </is>
       </c>
@@ -3732,7 +3728,7 @@
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰⌝</t>
+汰</t>
         </is>
       </c>
       <c r="O4" s="23"/>
@@ -3740,7 +3736,7 @@
       <c r="Q4" s="23"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧淋湳
+          <t xml:space="preserve">淋湳
 –</t>
         </is>
       </c>
@@ -3757,32 +3753,24 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∧
-–汰∽∼</t>
+          <t xml:space="preserve">–汰∼</t>
         </is>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏仲太
-仲
-⊏</t>
+          <t xml:space="preserve">仲太
+仲</t>
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -3792,10 +3780,8 @@
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林南∧
-–
-ﾉ
-‹</t>
+          <t xml:space="preserve">南林南
+–</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -3813,7 +3799,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢ʒ
+          <t xml:space="preserve">汰潢
 南潢</t>
         </is>
       </c>
@@ -3826,15 +3812,15 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰ʒ
-潢Z</t>
+          <t xml:space="preserve">潢汰
+潢</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ
-–太∽</t>
+          <t xml:space="preserve">南
+–太</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -3846,7 +3832,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧汰潢
+          <t xml:space="preserve">汰潢
 –㳞</t>
         </is>
       </c>
@@ -3859,8 +3845,8 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏㳞汰∽
-淋∧</t>
+          <t xml:space="preserve">㳞汰
+淋</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -3875,7 +3861,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 林南</t>
         </is>
       </c>
@@ -3885,7 +3871,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰∧</t>
+–汰</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -3899,7 +3885,7 @@
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢ʒ
+          <t xml:space="preserve">汰潢
 南潢</t>
         </is>
       </c>
@@ -3917,47 +3903,29 @@
     </row>
     <row r="8" ht="165.78" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ潢南潢
-–ﾉ
-‹</t>
+          <t xml:space="preserve">潢南潢
+–</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
@@ -3967,7 +3935,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧湳
+          <t xml:space="preserve">湳
 淋△</t>
         </is>
       </c>
@@ -3983,7 +3951,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧汰潢∼
+          <t xml:space="preserve">汰潢∼
 –㳞</t>
         </is>
       </c>
@@ -3997,33 +3965,24 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ʒ潢㳞</t>
+潢㳞</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21"/>
       <c r="K9" s="22"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ϟϟϟ
-ϟ
-ϟ
-ϟϟ
-‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰㳞
-⊏
+          <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–И
+          <t xml:space="preserve">–
 湳△</t>
         </is>
       </c>
@@ -4031,7 +3990,6 @@
       <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-ﾉ
 淋</t>
         </is>
       </c>
@@ -4043,7 +4001,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢ʒ
+          <t xml:space="preserve">汰潢
 南潢</t>
         </is>
       </c>
@@ -4052,7 +4010,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 –∼</t>
         </is>
       </c>
@@ -4065,7 +4023,7 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -4073,9 +4031,8 @@
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳⌝
-㳞
-⊏</t>
+          <t xml:space="preserve">湳
+㳞</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4088,15 +4045,14 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 姑</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4113,7 +4069,7 @@
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∧∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -4130,21 +4086,11 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ϟϟϟ
-ϟ
-ϟ
-ϟ
-ϟϟ
-‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰㳞
-⊏
+          <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
@@ -4161,22 +4107,18 @@
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="O12" s="22"/>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z∧</t>
-        </is>
-      </c>
+      <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
@@ -4192,7 +4134,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4200,7 +4142,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⊏㳞汰∽
+          <t xml:space="preserve">㳞汰
 淋</t>
         </is>
       </c>
@@ -4215,23 +4157,21 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ汰潢
-Z</t>
+          <t xml:space="preserve">汰潢</t>
         </is>
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳⌝
-㳞
-⊏</t>
+          <t xml:space="preserve">湳
+㳞</t>
         </is>
       </c>
       <c r="S13" s="23"/>
@@ -4244,23 +4184,18 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∧∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4275,22 +4210,20 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ汰潢
-Z</t>
+          <t xml:space="preserve">汰潢</t>
         </is>
       </c>
       <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="S14" s="24"/>

--- a/sheets/조재수대금교본/검수/긴 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/긴 아리랑.xlsx
@@ -3636,34 +3636,36 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
-㳞</t>
+          <t xml:space="preserve">湳淋ʒ
+㳞
+⊏</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-–</t>
+          <t xml:space="preserve">南ㄱㅂ
+–
+ﾉ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">汰潢ʒ
 南潢</t>
         </is>
       </c>
@@ -3676,13 +3678,14 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">ʒ∼</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢</t>
+          <t xml:space="preserve">汰潢
+Z</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3703,7 +3706,8 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢</t>
+          <t xml:space="preserve">ʒ汰潢
+Z</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3712,13 +3716,13 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–·</t>
+–И·</t>
         </is>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 林南</t>
         </is>
       </c>
@@ -3728,7 +3732,7 @@
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+∧汰⌝</t>
         </is>
       </c>
       <c r="O4" s="23"/>
@@ -3736,7 +3740,7 @@
       <c r="Q4" s="23"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋湳
+          <t xml:space="preserve">∧淋湳
 –</t>
         </is>
       </c>
@@ -3759,18 +3763,24 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–汰∼</t>
+          <t xml:space="preserve">Z∧
+–汰∽∼</t>
         </is>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲太
-仲</t>
+          <t xml:space="preserve">⊏仲太
+仲
+⊏</t>
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -3780,8 +3790,9 @@
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林南
-–</t>
+          <t xml:space="preserve">南林南∧
+–
+ﾉ</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -3799,7 +3810,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">汰潢ʒ
 南潢</t>
         </is>
       </c>
@@ -3812,15 +3823,15 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰
-潢</t>
+          <t xml:space="preserve">潢汰ʒ
+潢Z</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-–太</t>
+          <t xml:space="preserve">南ㄱ
+–太∽</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -3832,7 +3843,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∧汰潢
 –㳞</t>
         </is>
       </c>
@@ -3845,8 +3856,8 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰
-淋</t>
+          <t xml:space="preserve">⊏㳞汰∽
+淋∧</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -3861,7 +3872,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 林南</t>
         </is>
       </c>
@@ -3871,7 +3882,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰</t>
+–汰∧</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -3885,7 +3896,7 @@
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">汰潢ʒ
 南潢</t>
         </is>
       </c>
@@ -3903,14 +3914,22 @@
     </row>
     <row r="8" ht="165.78" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢南潢
-–</t>
+          <t xml:space="preserve">ʒ潢南潢
+–ﾉ</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -3920,7 +3939,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 姑</t>
         </is>
       </c>
@@ -3935,7 +3954,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">∧湳
 淋△</t>
         </is>
       </c>
@@ -3951,7 +3970,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢∼
+          <t xml:space="preserve">∧汰潢∼
 –㳞</t>
         </is>
       </c>
@@ -3965,24 +3984,32 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-潢㳞</t>
+ʒ潢㳞</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21"/>
       <c r="K9" s="22"/>
-      <c r="L9" s="21"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ϟϟϟ
+ϟ
+ϟ
+ϟϟ</t>
+        </is>
+      </c>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">∽汰㳞
+⊏
 –</t>
         </is>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–И
 湳△</t>
         </is>
       </c>
@@ -3990,6 +4017,7 @@
       <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
+ﾉ
 淋</t>
         </is>
       </c>
@@ -4001,7 +4029,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">汰潢ʒ
 南潢</t>
         </is>
       </c>
@@ -4010,7 +4038,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 –∼</t>
         </is>
       </c>
@@ -4023,7 +4051,7 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -4031,8 +4059,9 @@
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-㳞</t>
+          <t xml:space="preserve">湳⌝
+㳞
+⊏</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4045,7 +4074,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 姑</t>
         </is>
       </c>
@@ -4069,7 +4098,7 @@
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∧∼</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -4086,11 +4115,20 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ϟϟϟ
+ϟ
+ϟ
+ϟ
+ϟϟ</t>
+        </is>
+      </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">∽汰㳞
+⊏
 –</t>
         </is>
       </c>
@@ -4107,18 +4145,22 @@
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="O12" s="22"/>
-      <c r="P12" s="21"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z∧</t>
+        </is>
+      </c>
       <c r="Q12" s="22"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
@@ -4134,7 +4176,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4142,7 +4184,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰
+          <t xml:space="preserve">⊏㳞汰∽
 淋</t>
         </is>
       </c>
@@ -4157,21 +4199,23 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢</t>
+          <t xml:space="preserve">ʒ汰潢
+Z</t>
         </is>
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-㳞</t>
+          <t xml:space="preserve">湳⌝
+㳞
+⊏</t>
         </is>
       </c>
       <c r="S13" s="23"/>
@@ -4184,18 +4228,22 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∧∼</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4216,14 +4264,15 @@
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢</t>
+          <t xml:space="preserve">ʒ汰潢
+Z</t>
         </is>
       </c>
       <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="S14" s="24"/>

--- a/sheets/조재수대금교본/검수/긴 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/긴 아리랑.xlsx
@@ -3583,30 +3583,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="111.11" customHeight="true">
+    <row r="2" ht="114.29" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="165.78" customHeight="true">
+    <row r="3" ht="170.53" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="165.78" customHeight="true">
+    <row r="4" ht="170.53" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="165.78" customHeight="true">
+    <row r="5" ht="170.53" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="165.78" customHeight="true">
+    <row r="6" ht="170.53" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="165.78" customHeight="true">
+    <row r="7" ht="170.53" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
       <c r="R7" s="21"/>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="165.78" customHeight="true">
+    <row r="8" ht="170.53" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="165.78" customHeight="true">
+    <row r="9" ht="170.53" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="165.78" customHeight="true">
+    <row r="10" ht="170.53" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4068,7 +4068,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="165.78" customHeight="true">
+    <row r="11" ht="170.53" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="165.78" customHeight="true">
+    <row r="12" ht="170.53" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="165.78" customHeight="true">
+    <row r="13" ht="170.53" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="165.78" customHeight="true">
+    <row r="14" ht="170.53" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4283,6 +4283,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="36"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="35"/>
 </worksheet>
 </file>